--- a/www/flightdata/xlsx/eoss-291.xlsx
+++ b/www/flightdata/xlsx/eoss-291.xlsx
@@ -3822,7 +3822,7 @@
         <v>31353.86</v>
       </c>
       <c r="I2">
-        <v>669</v>
+        <v>500</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
